--- a/outputs/daily/hr_rankings_2026-09-30.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-30.xlsx
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>37.3</v>
       </c>
       <c r="R3" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -2204,7 +2204,7 @@
         <v>33.9</v>
       </c>
       <c r="R7" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>33.9</v>
       </c>
       <c r="R8" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S8" t="n">
         <v>94.90000000000001</v>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>33.9</v>
       </c>
       <c r="R9" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>37.3</v>
       </c>
       <c r="R11" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S11" t="n">
         <v>96.59999999999999</v>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>33.9</v>
       </c>
       <c r="R12" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S12" t="n">
         <v>76.2</v>
@@ -3786,12 +3786,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>37.3</v>
       </c>
       <c r="R23" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S23" t="n">
         <v>76.2</v>
@@ -6850,12 +6850,12 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -8592,7 +8592,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>37.3</v>
       </c>
       <c r="R30" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S30" t="n">
         <v>86.40000000000001</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>37.3</v>
       </c>
       <c r="R33" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S33" t="n">
         <v>94.90000000000001</v>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>33.9</v>
       </c>
       <c r="R34" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S34" t="n">
         <v>64.3</v>
@@ -9914,12 +9914,12 @@
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>37.3</v>
       </c>
       <c r="R39" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S39" t="n">
         <v>93.2</v>
@@ -11306,12 +11306,12 @@
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
@@ -11652,7 +11652,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>37.3</v>
       </c>
       <c r="R41" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S41" t="n">
         <v>64.3</v>
@@ -11862,12 +11862,12 @@
       </c>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI41" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>33.9</v>
       </c>
       <c r="R48" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S48" t="n">
         <v>52.4</v>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI48" t="inlineStr">
@@ -14188,7 +14188,7 @@
         <v>33.9</v>
       </c>
       <c r="R50" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S50" t="n">
         <v>86.40000000000001</v>
@@ -14374,12 +14374,12 @@
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
@@ -14679,52 +14679,52 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-30T21:00:00Z</t>
+          <t>2026-09-30T18:00:00Z</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -14742,23 +14742,23 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>49.9</v>
+        <v>15.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>20.7</v>
+        <v>32.1</v>
       </c>
       <c r="R52" t="n">
-        <v>41.6</v>
+        <v>53.9</v>
       </c>
       <c r="S52" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T52" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -14775,7 +14775,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 12.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.0% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -14843,112 +14843,112 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>70.93</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>35.49</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>86.17</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>0.3208</t>
+          <t>0.3597</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>0.1164</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr"/>
@@ -14959,56 +14959,56 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-30T18:00:00Z</t>
+          <t>2026-09-30T21:00:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -15022,23 +15022,23 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>15.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>32.1</v>
+        <v>20.7</v>
       </c>
       <c r="R53" t="n">
-        <v>53.4</v>
+        <v>41.6</v>
       </c>
       <c r="S53" t="n">
-        <v>96.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="T53" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
@@ -15108,12 +15108,12 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.0% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15123,112 +15123,112 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>70.93</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>35.49</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>86.17</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.3597</t>
+          <t>0.3208</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1164</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>37.3</v>
       </c>
       <c r="R58" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S58" t="n">
         <v>44.8</v>
@@ -16606,12 +16606,12 @@
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI58" t="inlineStr">
@@ -17252,7 +17252,7 @@
         <v>37.3</v>
       </c>
       <c r="R61" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S61" t="n">
         <v>52.4</v>
@@ -17438,12 +17438,12 @@
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI61" t="inlineStr">
@@ -19448,7 +19448,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>33.9</v>
       </c>
       <c r="R69" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S69" t="n">
         <v>44.8</v>
@@ -19658,12 +19658,12 @@
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
@@ -21446,7 +21446,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>37.3</v>
       </c>
       <c r="R3" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -21656,12 +21656,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -22582,7 +22582,7 @@
         <v>33.9</v>
       </c>
       <c r="R7" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -22768,12 +22768,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>33.9</v>
       </c>
       <c r="R8" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S8" t="n">
         <v>94.90000000000001</v>
@@ -23048,12 +23048,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -23118,7 +23118,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>33.9</v>
       </c>
       <c r="R9" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -23328,12 +23328,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -23674,7 +23674,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>37.3</v>
       </c>
       <c r="R11" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S11" t="n">
         <v>96.59999999999999</v>
@@ -23884,12 +23884,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -23954,7 +23954,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>33.9</v>
       </c>
       <c r="R12" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S12" t="n">
         <v>76.2</v>
@@ -24164,12 +24164,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-09-30.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-30.xlsx
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -17204,7 +17204,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
